--- a/excels/template.xlsx
+++ b/excels/template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\private\party-lottery\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\private\party-lottery\public\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,16 +36,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>工号</t>
+    <t>EmployeeID (工号)</t>
   </si>
   <si>
-    <t>姓名</t>
+    <t>Name (姓名)</t>
   </si>
   <si>
-    <t>部门</t>
+    <t>Department (部门)</t>
   </si>
   <si>
-    <t>头像</t>
+    <t>Avatar (头像)</t>
   </si>
 </sst>
 </file>
@@ -682,7 +682,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -690,7 +690,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1008,13 +1011,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="161" width="15" customWidth="1"/>
+    <col min="1" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
+    <col min="5" max="161" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1027,6 +1032,9 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="F14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
